--- a/input/16_measnonresource.xlsx
+++ b/input/16_measnonresource.xlsx
@@ -1,11 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29421"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29328"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="15" documentId="11_89478FA39BCAB048D3E75AD285600B733CED4083" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A9D46BB7-99CC-43D8-BE18-6BC3F1ACCBF5}"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://nv5inc-my.sharepoint.com/personal/andrewj_johnson_nv5_com/Documents/Documents/GitHub/market_inputs/input/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="21" documentId="11_89478FA39BCAB048D3E75AD285600B733CED4083" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0C24A138-1509-457F-BC5A-715F13AC8FF1}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3465" yWindow="3465" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -32,14 +37,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
   <si>
     <t>other_nonresource_benefit</t>
   </si>
   <si>
-    <t>test_utility</t>
-  </si>
-  <si>
     <t>Combined Energy and Capacity DRIPE</t>
   </si>
   <si>
@@ -71,6 +73,21 @@
   </si>
   <si>
     <t>West Penn Power</t>
+  </si>
+  <si>
+    <t>test_utility_1</t>
+  </si>
+  <si>
+    <t>test_utility_2</t>
+  </si>
+  <si>
+    <t>test_utility_3</t>
+  </si>
+  <si>
+    <t>none</t>
+  </si>
+  <si>
+    <t>utility</t>
   </si>
 </sst>
 </file>
@@ -81,7 +98,7 @@
     <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.000_);[Red]\(&quot;$&quot;#,##0.000\)"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -100,6 +117,12 @@
       <sz val="10"/>
       <name val="Helvetica-Narrow"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -130,7 +153,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -139,6 +162,9 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Currency" xfId="1" builtinId="4"/>
@@ -475,24 +501,54 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:B5"/>
   <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="23.140625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:2">
-      <c r="A1" s="2"/>
+      <c r="A1" s="2" t="s">
+        <v>16</v>
+      </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="B2" s="3">
         <v>2.5394644444743365E-2</v>
       </c>
     </row>
+    <row r="3" spans="1:2">
+      <c r="A3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" s="3">
+        <v>2.5394644444743365E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" s="3">
+        <v>2.5394644444743365E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" s="3">
+        <v>2.5394644444743365E-2</v>
+      </c>
+    </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -504,23 +560,23 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="2"/>
       <c r="B3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B4">
         <v>1</v>
@@ -537,7 +593,7 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B5" s="3">
         <v>2.5394644444743365E-2</v>
@@ -554,7 +610,7 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B6" s="3">
         <v>2.7053076111871785E-2</v>
@@ -571,7 +627,7 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B7" s="3">
         <v>1.9511825155790315E-2</v>
@@ -588,7 +644,7 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B8" s="3">
         <v>2.5412383223072176E-2</v>
@@ -605,7 +661,7 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B9" s="3">
         <v>2.7152504600988368E-2</v>
@@ -622,7 +678,7 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B10" s="3">
         <v>1.8204500674793126E-2</v>
@@ -639,7 +695,7 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B11" s="3">
         <v>1.7861451414049306E-2</v>
@@ -669,12 +725,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100B011C3FEFFEFCF44990405A8404263A2" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3dc4baf5bca6f50981051f1202939c23">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="79a1cdf2-2d4f-42d7-aee4-ff0e208e0f4a" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="1497dbabdd8844cfa90d09d2bdc2ce45" ns2:_="">
     <xsd:import namespace="79a1cdf2-2d4f-42d7-aee4-ff0e208e0f4a"/>
@@ -818,14 +868,43 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3FA01326-7EAB-4685-9F0B-DB95BAA1835D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3FA01326-7EAB-4685-9F0B-DB95BAA1835D}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7DFF6699-07CF-45A8-84D7-C26E59057556}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7781F1F5-604D-4A01-B7C6-87E830B93F03}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="79a1cdf2-2d4f-42d7-aee4-ff0e208e0f4a"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7781F1F5-604D-4A01-B7C6-87E830B93F03}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7DFF6699-07CF-45A8-84D7-C26E59057556}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/input/16_measnonresource.xlsx
+++ b/input/16_measnonresource.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://nv5inc-my.sharepoint.com/personal/andrewj_johnson_nv5_com/Documents/Documents/GitHub/market_inputs/input/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="21" documentId="11_89478FA39BCAB048D3E75AD285600B733CED4083" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0C24A138-1509-457F-BC5A-715F13AC8FF1}"/>
+  <xr:revisionPtr revIDLastSave="26" documentId="11_89478FA39BCAB048D3E75AD285600B733CED4083" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{072FA816-1204-4EAF-8306-EB4D0886057F}"/>
   <bookViews>
     <workbookView xWindow="3465" yWindow="3465" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -153,7 +153,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -162,9 +162,6 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Currency" xfId="1" builtinId="4"/>
@@ -504,6 +501,7 @@
   <dimension ref="A1:B5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
+    <col min="1" max="1" width="16" customWidth="1"/>
     <col min="2" max="2" width="23.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -528,7 +526,7 @@
         <v>13</v>
       </c>
       <c r="B3" s="3">
-        <v>2.5394644444743365E-2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -536,15 +534,15 @@
         <v>14</v>
       </c>
       <c r="B4" s="3">
-        <v>2.5394644444743365E-2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:2">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="1" t="s">
         <v>15</v>
       </c>
       <c r="B5" s="3">
-        <v>2.5394644444743365E-2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
